--- a/Korp/Filial/2026-06/Fechamento_Folha_Korp_Filial_06-2026.xlsx
+++ b/Korp/Filial/2026-06/Fechamento_Folha_Korp_Filial_06-2026.xlsx
@@ -529,9 +529,8 @@
           <t>Salários a Pagar</t>
         </is>
       </c>
-      <c r="C5" s="5">
-        <f>'06-2026'!F5</f>
-        <v/>
+      <c r="C5" s="5" t="n">
+        <v>78617.06</v>
       </c>
     </row>
     <row r="6">
@@ -545,9 +544,8 @@
           <t>Indenizações Trabalhistas (rescisões)</t>
         </is>
       </c>
-      <c r="C6" s="5">
-        <f>'06-2026'!F6</f>
-        <v/>
+      <c r="C6" s="5" t="n">
+        <v>2114.87</v>
       </c>
     </row>
     <row r="7">
@@ -561,9 +559,8 @@
           <t>Férias a Pagar</t>
         </is>
       </c>
-      <c r="C7" s="5">
-        <f>'06-2026'!F7</f>
-        <v/>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -577,9 +574,8 @@
           <t>Estágios a pagar</t>
         </is>
       </c>
-      <c r="C8" s="5">
-        <f>'06-2026'!F8</f>
-        <v/>
+      <c r="C8" s="5" t="n">
+        <v>9182</v>
       </c>
     </row>
     <row r="9">
@@ -593,9 +589,8 @@
           <t>FGTS a Recolher</t>
         </is>
       </c>
-      <c r="C9" s="5">
-        <f>'06-2026'!F9</f>
-        <v/>
+      <c r="C9" s="5" t="n">
+        <v>7466.04</v>
       </c>
     </row>
     <row r="10">
@@ -609,9 +604,8 @@
           <t>INSS a Recolher</t>
         </is>
       </c>
-      <c r="C10" s="5">
-        <f>'06-2026'!F10</f>
-        <v/>
+      <c r="C10" s="5" t="n">
+        <v>34648.06</v>
       </c>
     </row>
     <row r="11">
@@ -625,9 +619,8 @@
           <t>IRRF a Recolher s/ Folha</t>
         </is>
       </c>
-      <c r="C11" s="5">
-        <f>'06-2026'!F11</f>
-        <v/>
+      <c r="C11" s="5" t="n">
+        <v>833.86</v>
       </c>
     </row>
     <row r="12">
@@ -641,9 +634,8 @@
           <t>Empréstimo a Funcionário (consignado)</t>
         </is>
       </c>
-      <c r="C12" s="5">
-        <f>'06-2026'!F12</f>
-        <v/>
+      <c r="C12" s="5" t="n">
+        <v>2248.56</v>
       </c>
     </row>
     <row r="13">
@@ -657,9 +649,8 @@
           <t>Adiantamento de Férias (ativo)</t>
         </is>
       </c>
-      <c r="C13" s="5">
-        <f>'06-2026'!F13</f>
-        <v/>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -668,9 +659,10 @@
           <t>Confere com a folha?</t>
         </is>
       </c>
-      <c r="C14" s="7">
-        <f>IF(COUNTIF('06-2026'!H5:H13,"Não")=0,"Sim","Não")</f>
-        <v/>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -779,16 +771,16 @@
       <c r="E5" s="10" t="n">
         <v>-4104</v>
       </c>
-      <c r="F5" s="10">
-        <f>D5+E5</f>
-        <v/>
+      <c r="F5" s="10" t="n">
+        <v>78617.06</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="8">
-        <f>IF(ABS(C5+G5-F5)&lt;1,"Sim","Não")</f>
-        <v/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
@@ -816,16 +808,16 @@
       <c r="E6" s="10" t="n">
         <v>132.47</v>
       </c>
-      <c r="F6" s="10">
-        <f>D6+E6</f>
-        <v/>
+      <c r="F6" s="10" t="n">
+        <v>2114.87</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>-5583.5</v>
       </c>
-      <c r="H6" s="8">
-        <f>IF(ABS(C6+G6-F6)&lt;1,"Sim","Não")</f>
-        <v/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -853,16 +845,16 @@
       <c r="E7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="10">
-        <f>D7+E7</f>
-        <v/>
+      <c r="F7" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="8">
-        <f>IF(ABS(C7+G7-F7)&lt;1,"Sim","Não")</f>
-        <v/>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -890,16 +882,16 @@
       <c r="E8" s="10" t="n">
         <v>6790</v>
       </c>
-      <c r="F8" s="10">
-        <f>D8+E8</f>
-        <v/>
+      <c r="F8" s="10" t="n">
+        <v>9182</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="8">
-        <f>IF(ABS(C8+G8-F8)&lt;1,"Sim","Não")</f>
-        <v/>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -927,16 +919,16 @@
       <c r="E9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="10">
-        <f>D9+E9</f>
-        <v/>
+      <c r="F9" s="10" t="n">
+        <v>7466.04</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>-537.65</v>
       </c>
-      <c r="H9" s="8">
-        <f>IF(ABS(C9+G9-F9)&lt;1,"Sim","Não")</f>
-        <v/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
@@ -964,16 +956,16 @@
       <c r="E10" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="10">
-        <f>D10+E10</f>
-        <v/>
+      <c r="F10" s="10" t="n">
+        <v>34648.06</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>-315.15</v>
       </c>
-      <c r="H10" s="8">
-        <f>IF(ABS(C10+G10-F10)&lt;1,"Sim","Não")</f>
-        <v/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1001,16 +993,16 @@
       <c r="E11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="10">
-        <f>D11+E11</f>
-        <v/>
+      <c r="F11" s="10" t="n">
+        <v>833.86</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="8">
-        <f>IF(ABS(C11+G11-F11)&lt;1,"Sim","Não")</f>
-        <v/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="I11" s="11" t="inlineStr"/>
     </row>
@@ -1034,16 +1026,16 @@
       <c r="E12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="10">
-        <f>D12+E12</f>
-        <v/>
+      <c r="F12" s="10" t="n">
+        <v>2248.56</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="8">
-        <f>IF(ABS(C12+G12-F12)&lt;1,"Sim","Não")</f>
-        <v/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="I12" s="11" t="inlineStr"/>
     </row>
@@ -1067,16 +1059,16 @@
       <c r="E13" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="10">
-        <f>D13+E13</f>
-        <v/>
+      <c r="F13" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="8">
-        <f>IF(ABS(C13+G13-F13)&lt;1,"Sim","Não")</f>
-        <v/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
@@ -1097,21 +1089,17 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C16" s="12">
-        <f>C5+C6+C7+C8</f>
-        <v/>
-      </c>
-      <c r="D16" s="12">
-        <f>D5+D6+D7+D8</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
-        <f>F5+F6+F7+F8</f>
-        <v/>
-      </c>
-      <c r="G16" s="12">
-        <f>G5+G6+G7+G8</f>
-        <v/>
+      <c r="C16" s="12" t="n">
+        <v>95497.42999999999</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>87095.46000000001</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>89913.92999999999</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>-5583.5</v>
       </c>
     </row>
   </sheetData>
